--- a/Excel001_2.xlsx
+++ b/Excel001_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work_LinhLT\Contrack_new_version\ver 5.0.1\01.New Function\02.Envidence\File test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thuylinh.le\OneDrive - 株式会社ベリサーブ\Desktop\Contrack\5.0.1\6944_Envidence\New_L_project020\branches01\5.0.0_Github_7351_7352_repo01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBE06CD-78FB-47E9-A5C8-96695B009DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB5F587-F65F-44B0-B272-E2304566A52E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="0" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="A1" sheetId="8" r:id="rId1"/>
@@ -547,7 +547,9 @@
     </row>
     <row r="7" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="C7" s="1">
+        <v>66666</v>
+      </c>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
